--- a/Framework_Inputs/Master_Workbook/Master_Excel.xlsx
+++ b/Framework_Inputs/Master_Workbook/Master_Excel.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nftuser\Documents\FrameworkRepo\Framework_Inputs\Master_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B21BF741-2424-446C-87AF-BBA2622CD837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99618582-C3E3-42D7-A9FC-709F060B9E86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{4B37E54E-E88F-4F7A-959C-8B3242D470DF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{44A5E5BC-6667-4173-B999-0E2C38860BF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Control" sheetId="4" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="109">
   <si>
     <t>Test Plan</t>
   </si>
@@ -82,6 +82,9 @@
     <t>JMX Path</t>
   </si>
   <si>
+    <t>Execution Scenario</t>
+  </si>
+  <si>
     <t>Stage</t>
   </si>
   <si>
@@ -91,10 +94,10 @@
     <t>Load Generator IP</t>
   </si>
   <si>
-    <t>C:\Users\nftuser\Documents\FrameworkRepo\Framework_Inputs\petclinic_test_plan.jmx</t>
-  </si>
-  <si>
-    <t>Nil</t>
+    <t>C:\Users\nftuser\Documents\FrameworkRepo\Framework_Inputs\Scripts\CBSTestPlan.jmx</t>
+  </si>
+  <si>
+    <t>10% Volume</t>
   </si>
   <si>
     <t>R001</t>
@@ -106,7 +109,22 @@
     <t>127.0.0.1</t>
   </si>
   <si>
-    <t>petclinic_test_plan_Duration</t>
+    <t>CBS</t>
+  </si>
+  <si>
+    <t>CBSTestPlan_Duration</t>
+  </si>
+  <si>
+    <t>C:\Users\nftuser\Documents\FrameworkRepo\Framework_Inputs\Scripts\IBTestPlan_Final.jmx</t>
+  </si>
+  <si>
+    <t>30% Volume</t>
+  </si>
+  <si>
+    <t>IB</t>
+  </si>
+  <si>
+    <t>IBTestPlan_Final_Duration</t>
   </si>
   <si>
     <t>OperatingSystem</t>
@@ -161,6 +179,192 @@
   </si>
   <si>
     <t>httpclient.socket.https.cps</t>
+  </si>
+  <si>
+    <t>CBSTestPlan</t>
+  </si>
+  <si>
+    <t>IB_Add</t>
+  </si>
+  <si>
+    <t>IB_Change</t>
+  </si>
+  <si>
+    <t>IB_Remove</t>
+  </si>
+  <si>
+    <t>IB_Create</t>
+  </si>
+  <si>
+    <t>IB_Update</t>
+  </si>
+  <si>
+    <t>IB_Delete</t>
+  </si>
+  <si>
+    <t>IB_AddThread</t>
+  </si>
+  <si>
+    <t>IB_AddLoop</t>
+  </si>
+  <si>
+    <t>IB_AddPacing</t>
+  </si>
+  <si>
+    <t>IB_AddRampUp</t>
+  </si>
+  <si>
+    <t>IB_ChangeThread</t>
+  </si>
+  <si>
+    <t>IB_ChangeLoop</t>
+  </si>
+  <si>
+    <t>IB_ChangePacing</t>
+  </si>
+  <si>
+    <t>IB_ChangeRampUp</t>
+  </si>
+  <si>
+    <t>IB_RemoveThread</t>
+  </si>
+  <si>
+    <t>IB_RemoveLoop</t>
+  </si>
+  <si>
+    <t>IB_RemovePacing</t>
+  </si>
+  <si>
+    <t>IB_RemoveRampUp</t>
+  </si>
+  <si>
+    <t>IB_CreateThread</t>
+  </si>
+  <si>
+    <t>IB_CreateLoop</t>
+  </si>
+  <si>
+    <t>IB_CreatePacing</t>
+  </si>
+  <si>
+    <t>IB_CreateRampUp</t>
+  </si>
+  <si>
+    <t>IB_UpdateThread</t>
+  </si>
+  <si>
+    <t>IB_UpdateLoop</t>
+  </si>
+  <si>
+    <t>IB_UpdatePacing</t>
+  </si>
+  <si>
+    <t>IB_UpdateRampUp</t>
+  </si>
+  <si>
+    <t>IB_DeleteThread</t>
+  </si>
+  <si>
+    <t>IB_DeleteLoop</t>
+  </si>
+  <si>
+    <t>IB_DeletePacing</t>
+  </si>
+  <si>
+    <t>IB_DeleteRampUp</t>
+  </si>
+  <si>
+    <t>IBTestPlan_Final</t>
+  </si>
+  <si>
+    <t>Create</t>
+  </si>
+  <si>
+    <t>Create_User</t>
+  </si>
+  <si>
+    <t>Update</t>
+  </si>
+  <si>
+    <t>Update_User</t>
+  </si>
+  <si>
+    <t>Delete</t>
+  </si>
+  <si>
+    <t>Delete_User</t>
+  </si>
+  <si>
+    <t>CreateThread</t>
+  </si>
+  <si>
+    <t>CreateLoop</t>
+  </si>
+  <si>
+    <t>CreatePacing</t>
+  </si>
+  <si>
+    <t>CreateRampUp</t>
+  </si>
+  <si>
+    <t>Create_UserThread</t>
+  </si>
+  <si>
+    <t>Create_UserLoop</t>
+  </si>
+  <si>
+    <t>Create_UserPacing</t>
+  </si>
+  <si>
+    <t>Create_UserRampUp</t>
+  </si>
+  <si>
+    <t>UpdateThread</t>
+  </si>
+  <si>
+    <t>UpdateLoop</t>
+  </si>
+  <si>
+    <t>UpdatePacing</t>
+  </si>
+  <si>
+    <t>UpdateRampUp</t>
+  </si>
+  <si>
+    <t>Update_UserThread</t>
+  </si>
+  <si>
+    <t>Update_UserLoop</t>
+  </si>
+  <si>
+    <t>Update_UserPacing</t>
+  </si>
+  <si>
+    <t>Update_UserRampUp</t>
+  </si>
+  <si>
+    <t>DeleteThread</t>
+  </si>
+  <si>
+    <t>DeleteLoop</t>
+  </si>
+  <si>
+    <t>DeletePacing</t>
+  </si>
+  <si>
+    <t>DeleteRampUp</t>
+  </si>
+  <si>
+    <t>Delete_UserThread</t>
+  </si>
+  <si>
+    <t>Delete_UserLoop</t>
+  </si>
+  <si>
+    <t>Delete_UserPacing</t>
+  </si>
+  <si>
+    <t>Delete_UserRampUp</t>
   </si>
 </sst>
 </file>
@@ -235,9 +439,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -562,49 +769,67 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3245BF5-21C2-4D4A-932F-AE47D4E1859F}">
-  <dimension ref="A1:E2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07CF1D6C-402C-41FB-BBEE-7387941CE7AD}">
+  <sheetPr codeName="Sheet4"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="76" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="81.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>16</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>21</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -613,8 +838,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5D953D4-1A20-4773-B113-C9A522312551}">
-  <dimension ref="A1:C14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D81B77CD-8B8B-4895-A4C4-8B0660CAD414}">
+  <sheetPr codeName="Sheet3"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.85546875" bestFit="1" customWidth="1"/>
@@ -623,99 +849,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C2" s="1">
-        <v>360</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="C3" s="1">
+        <v>3600</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="1">
-        <v>8086</v>
+        <v>30</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="1" t="s">
         <v>30</v>
+      </c>
+      <c r="C6" s="1">
+        <v>8086</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="1" t="b">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C9" s="1" t="b">
         <v>1</v>
@@ -723,10 +949,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C10" s="1" t="b">
         <v>1</v>
@@ -734,10 +960,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C11" s="1" t="b">
         <v>1</v>
@@ -745,34 +971,45 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>38</v>
+        <v>30</v>
+      </c>
+      <c r="C12" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="1">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="1">
         <v>0</v>
       </c>
     </row>
@@ -782,13 +1019,14 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{222A18B9-FFDC-4320-B1F6-584C2B3485F8}">
-  <dimension ref="A1:K2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC63F97B-C549-44F9-94FC-7C8A96B8D06D}">
+  <sheetPr codeName="Sheet2"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
@@ -800,52 +1038,459 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
+      <c r="A2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="2">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G2" s="2">
+        <v>5</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I2" s="2">
+        <v>10</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K2" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="2">
+        <v>2</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G3" s="2">
+        <v>15</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I3" s="2">
+        <v>10</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K3" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="2">
+        <v>3</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G4" s="2">
+        <v>12</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I4" s="2">
+        <v>10</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K4" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G5" s="2">
+        <v>12</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I5" s="2">
+        <v>10</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="K5" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E6" s="2">
+        <v>2</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G6" s="2">
+        <v>10</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I6" s="2">
+        <v>10</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K6" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E7" s="2">
+        <v>2</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G7" s="2">
+        <v>8</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I7" s="2">
+        <v>10</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="K7" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E8" s="2">
+        <v>3</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G8" s="2">
+        <v>25</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I8" s="2">
+        <v>10</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="K8" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E9" s="2">
+        <v>9</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G9" s="2">
+        <v>4</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I9" s="2">
+        <v>10</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="K9" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E10" s="2">
+        <v>6</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G10" s="2">
+        <v>15</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I10" s="2">
+        <v>10</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K10" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E11" s="2">
+        <v>12</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G11" s="2">
+        <v>9</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I11" s="2">
+        <v>10</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="K11" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E12" s="2">
+        <v>6</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G12" s="2">
+        <v>9</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="I12" s="2">
+        <v>10</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="K12" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E13" s="2">
+        <v>3</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G13" s="2">
+        <v>32</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="I13" s="2">
+        <v>10</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K13" s="2">
+        <v>36</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Framework_Inputs/Master_Workbook/Master_Excel.xlsx
+++ b/Framework_Inputs/Master_Workbook/Master_Excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nftuser\Documents\FrameworkRepo\Framework_Inputs\Master_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99618582-C3E3-42D7-A9FC-709F060B9E86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9D96FD2-C8F7-4CB2-88FE-3246A4D31243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{44A5E5BC-6667-4173-B999-0E2C38860BF2}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="108">
   <si>
     <t>Test Plan</t>
   </si>
@@ -98,9 +98,6 @@
   </si>
   <si>
     <t>10% Volume</t>
-  </si>
-  <si>
-    <t>R001</t>
   </si>
   <si>
     <t>Yes</t>
@@ -805,31 +802,31 @@
       <c r="B2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="1">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -861,10 +858,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" s="1">
         <v>3600</v>
@@ -872,10 +869,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C3" s="1">
         <v>3600</v>
@@ -883,32 +880,32 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C6" s="1">
         <v>8086</v>
@@ -916,32 +913,32 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C9" s="1" t="b">
         <v>1</v>
@@ -949,10 +946,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10" s="1" t="b">
         <v>1</v>
@@ -960,10 +957,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="1" t="b">
         <v>1</v>
@@ -971,10 +968,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C12" s="1" t="b">
         <v>1</v>
@@ -982,21 +979,21 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C14" s="1">
         <v>0</v>
@@ -1004,10 +1001,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C15" s="1">
         <v>0</v>
@@ -1074,34 +1071,34 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E2" s="2">
         <v>4</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G2" s="2">
         <v>5</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I2" s="2">
         <v>10</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K2" s="2">
         <v>12</v>
@@ -1109,34 +1106,34 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E3" s="2">
         <v>2</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G3" s="2">
         <v>15</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I3" s="2">
         <v>10</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K3" s="2">
         <v>18</v>
@@ -1144,34 +1141,34 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E4" s="2">
         <v>3</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G4" s="2">
         <v>12</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I4" s="2">
         <v>10</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K4" s="2">
         <v>10</v>
@@ -1179,34 +1176,34 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E5" s="2">
         <v>1</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G5" s="2">
         <v>12</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I5" s="2">
         <v>10</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K5" s="2">
         <v>12</v>
@@ -1214,34 +1211,34 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E6" s="2">
         <v>2</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G6" s="2">
         <v>10</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I6" s="2">
         <v>10</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K6" s="2">
         <v>24</v>
@@ -1249,34 +1246,34 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E7" s="2">
         <v>2</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G7" s="2">
         <v>8</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I7" s="2">
         <v>10</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K7" s="2">
         <v>24</v>
@@ -1284,34 +1281,34 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>79</v>
-      </c>
       <c r="C8" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E8" s="2">
         <v>3</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G8" s="2">
         <v>25</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I8" s="2">
         <v>10</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K8" s="2">
         <v>36</v>
@@ -1319,34 +1316,34 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E9" s="2">
         <v>9</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G9" s="2">
         <v>4</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I9" s="2">
         <v>10</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K9" s="2">
         <v>75</v>
@@ -1354,34 +1351,34 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E10" s="2">
         <v>6</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G10" s="2">
         <v>15</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I10" s="2">
         <v>10</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K10" s="2">
         <v>72</v>
@@ -1389,34 +1386,34 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E11" s="2">
         <v>12</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G11" s="2">
         <v>9</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I11" s="2">
         <v>10</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K11" s="2">
         <v>90</v>
@@ -1424,34 +1421,34 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E12" s="2">
         <v>6</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G12" s="2">
         <v>9</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I12" s="2">
         <v>10</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K12" s="2">
         <v>72</v>
@@ -1459,34 +1456,34 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E13" s="2">
         <v>3</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G13" s="2">
         <v>32</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I13" s="2">
         <v>10</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K13" s="2">
         <v>36</v>

--- a/Framework_Inputs/Master_Workbook/Master_Excel.xlsx
+++ b/Framework_Inputs/Master_Workbook/Master_Excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nftuser\Documents\FrameworkRepo\Framework_Inputs\Master_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9D96FD2-C8F7-4CB2-88FE-3246A4D31243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6DA02F6-75D4-4B02-A800-FFB01EC2FE55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{44A5E5BC-6667-4173-B999-0E2C38860BF2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{E6EFDEBD-5522-4CFF-85A8-02F11CBA0D33}"/>
   </bookViews>
   <sheets>
     <sheet name="Control" sheetId="4" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="57">
   <si>
     <t>Test Plan</t>
   </si>
@@ -94,10 +94,10 @@
     <t>Load Generator IP</t>
   </si>
   <si>
-    <t>C:\Users\nftuser\Documents\FrameworkRepo\Framework_Inputs\Scripts\CBSTestPlan.jmx</t>
-  </si>
-  <si>
-    <t>10% Volume</t>
+    <t>C:\Users\nftuser\Documents\FrameworkRepo\Framework_Inputs\Scripts\petclinictestplan.jmx</t>
+  </si>
+  <si>
+    <t>30% Volume</t>
   </si>
   <si>
     <t>Yes</t>
@@ -106,22 +106,7 @@
     <t>127.0.0.1</t>
   </si>
   <si>
-    <t>CBS</t>
-  </si>
-  <si>
-    <t>CBSTestPlan_Duration</t>
-  </si>
-  <si>
-    <t>C:\Users\nftuser\Documents\FrameworkRepo\Framework_Inputs\Scripts\IBTestPlan_Final.jmx</t>
-  </si>
-  <si>
-    <t>30% Volume</t>
-  </si>
-  <si>
-    <t>IB</t>
-  </si>
-  <si>
-    <t>IBTestPlan_Final_Duration</t>
+    <t>petclinictestplan_Duration</t>
   </si>
   <si>
     <t>OperatingSystem</t>
@@ -178,190 +163,52 @@
     <t>httpclient.socket.https.cps</t>
   </si>
   <si>
-    <t>CBSTestPlan</t>
-  </si>
-  <si>
-    <t>IB_Add</t>
-  </si>
-  <si>
-    <t>IB_Change</t>
-  </si>
-  <si>
-    <t>IB_Remove</t>
-  </si>
-  <si>
-    <t>IB_Create</t>
-  </si>
-  <si>
-    <t>IB_Update</t>
-  </si>
-  <si>
-    <t>IB_Delete</t>
-  </si>
-  <si>
-    <t>IB_AddThread</t>
-  </si>
-  <si>
-    <t>IB_AddLoop</t>
-  </si>
-  <si>
-    <t>IB_AddPacing</t>
-  </si>
-  <si>
-    <t>IB_AddRampUp</t>
-  </si>
-  <si>
-    <t>IB_ChangeThread</t>
-  </si>
-  <si>
-    <t>IB_ChangeLoop</t>
-  </si>
-  <si>
-    <t>IB_ChangePacing</t>
-  </si>
-  <si>
-    <t>IB_ChangeRampUp</t>
-  </si>
-  <si>
-    <t>IB_RemoveThread</t>
-  </si>
-  <si>
-    <t>IB_RemoveLoop</t>
-  </si>
-  <si>
-    <t>IB_RemovePacing</t>
-  </si>
-  <si>
-    <t>IB_RemoveRampUp</t>
-  </si>
-  <si>
-    <t>IB_CreateThread</t>
-  </si>
-  <si>
-    <t>IB_CreateLoop</t>
-  </si>
-  <si>
-    <t>IB_CreatePacing</t>
-  </si>
-  <si>
-    <t>IB_CreateRampUp</t>
-  </si>
-  <si>
-    <t>IB_UpdateThread</t>
-  </si>
-  <si>
-    <t>IB_UpdateLoop</t>
-  </si>
-  <si>
-    <t>IB_UpdatePacing</t>
-  </si>
-  <si>
-    <t>IB_UpdateRampUp</t>
-  </si>
-  <si>
-    <t>IB_DeleteThread</t>
-  </si>
-  <si>
-    <t>IB_DeleteLoop</t>
-  </si>
-  <si>
-    <t>IB_DeletePacing</t>
-  </si>
-  <si>
-    <t>IB_DeleteRampUp</t>
-  </si>
-  <si>
-    <t>IBTestPlan_Final</t>
-  </si>
-  <si>
-    <t>Create</t>
-  </si>
-  <si>
-    <t>Create_User</t>
-  </si>
-  <si>
-    <t>Update</t>
-  </si>
-  <si>
-    <t>Update_User</t>
-  </si>
-  <si>
-    <t>Delete</t>
-  </si>
-  <si>
-    <t>Delete_User</t>
-  </si>
-  <si>
-    <t>CreateThread</t>
-  </si>
-  <si>
-    <t>CreateLoop</t>
-  </si>
-  <si>
-    <t>CreatePacing</t>
-  </si>
-  <si>
-    <t>CreateRampUp</t>
-  </si>
-  <si>
-    <t>Create_UserThread</t>
-  </si>
-  <si>
-    <t>Create_UserLoop</t>
-  </si>
-  <si>
-    <t>Create_UserPacing</t>
-  </si>
-  <si>
-    <t>Create_UserRampUp</t>
-  </si>
-  <si>
-    <t>UpdateThread</t>
-  </si>
-  <si>
-    <t>UpdateLoop</t>
-  </si>
-  <si>
-    <t>UpdatePacing</t>
-  </si>
-  <si>
-    <t>UpdateRampUp</t>
-  </si>
-  <si>
-    <t>Update_UserThread</t>
-  </si>
-  <si>
-    <t>Update_UserLoop</t>
-  </si>
-  <si>
-    <t>Update_UserPacing</t>
-  </si>
-  <si>
-    <t>Update_UserRampUp</t>
-  </si>
-  <si>
-    <t>DeleteThread</t>
-  </si>
-  <si>
-    <t>DeleteLoop</t>
-  </si>
-  <si>
-    <t>DeletePacing</t>
-  </si>
-  <si>
-    <t>DeleteRampUp</t>
-  </si>
-  <si>
-    <t>Delete_UserThread</t>
-  </si>
-  <si>
-    <t>Delete_UserLoop</t>
-  </si>
-  <si>
-    <t>Delete_UserPacing</t>
-  </si>
-  <si>
-    <t>Delete_UserRampUp</t>
+    <t>petclinictestplan</t>
+  </si>
+  <si>
+    <t>Home_Page</t>
+  </si>
+  <si>
+    <t>Search _For_Vets</t>
+  </si>
+  <si>
+    <t>Owners</t>
+  </si>
+  <si>
+    <t>Home_PageThread</t>
+  </si>
+  <si>
+    <t>Home_PageLoop</t>
+  </si>
+  <si>
+    <t>Home_PagePacing</t>
+  </si>
+  <si>
+    <t>Home_PageRampUp</t>
+  </si>
+  <si>
+    <t>Search _For_VetsThread</t>
+  </si>
+  <si>
+    <t>Search _For_VetsLoop</t>
+  </si>
+  <si>
+    <t>Search _For_VetsPacing</t>
+  </si>
+  <si>
+    <t>Search _For_VetsRampUp</t>
+  </si>
+  <si>
+    <t>OwnersThread</t>
+  </si>
+  <si>
+    <t>OwnersLoop</t>
+  </si>
+  <si>
+    <t>OwnersPacing</t>
+  </si>
+  <si>
+    <t>OwnersRampUp</t>
   </si>
 </sst>
 </file>
@@ -766,12 +613,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07CF1D6C-402C-41FB-BBEE-7387941CE7AD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1FB16C5-4791-456B-A841-295FAB02979B}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="81.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="80.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.85546875" bestFit="1" customWidth="1"/>
@@ -812,32 +659,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="1">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D81B77CD-8B8B-4895-A4C4-8B0660CAD414}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D86495F-CA2A-45F3-88B0-759EE8980182}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.85546875" bestFit="1" customWidth="1"/>
@@ -858,10 +688,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C2" s="1">
         <v>3600</v>
@@ -869,76 +699,76 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="1">
-        <v>3600</v>
+        <v>24</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
+      </c>
+      <c r="C5" s="1">
+        <v>8086</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="1">
-        <v>8086</v>
+        <v>24</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>37</v>
+        <v>24</v>
+      </c>
+      <c r="C8" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C9" s="1" t="b">
         <v>1</v>
@@ -946,10 +776,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C10" s="1" t="b">
         <v>1</v>
@@ -957,10 +787,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C11" s="1" t="b">
         <v>1</v>
@@ -968,45 +798,34 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="1" t="b">
-        <v>1</v>
+        <v>24</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>43</v>
+        <v>24</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1016,21 +835,21 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC63F97B-C549-44F9-94FC-7C8A96B8D06D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57E99092-B274-43C6-83BB-66E13CE8B82B}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1071,422 +890,107 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E2" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="G2" s="2">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="I2" s="2">
         <v>10</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="K2" s="2">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E3" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G3" s="2">
         <v>15</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="I3" s="2">
         <v>10</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="K3" s="2">
-        <v>18</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="E4" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="G4" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="I4" s="2">
         <v>10</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="K4" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E5" s="2">
-        <v>1</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="G5" s="2">
-        <v>12</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I5" s="2">
-        <v>10</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="K5" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E6" s="2">
-        <v>2</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="G6" s="2">
-        <v>10</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="I6" s="2">
-        <v>10</v>
-      </c>
-      <c r="J6" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="K6" s="2">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" s="2">
-        <v>2</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="G7" s="2">
-        <v>8</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="I7" s="2">
-        <v>10</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="K7" s="2">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E8" s="2">
-        <v>3</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="G8" s="2">
-        <v>25</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="I8" s="2">
-        <v>10</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="K8" s="2">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E9" s="2">
-        <v>9</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G9" s="2">
-        <v>4</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="I9" s="2">
-        <v>10</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="K9" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E10" s="2">
-        <v>6</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="G10" s="2">
-        <v>15</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="I10" s="2">
-        <v>10</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="K10" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="E11" s="2">
-        <v>12</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G11" s="2">
-        <v>9</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="I11" s="2">
-        <v>10</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="K11" s="2">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E12" s="2">
-        <v>6</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G12" s="2">
-        <v>9</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I12" s="2">
-        <v>10</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="K12" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E13" s="2">
-        <v>3</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="G13" s="2">
-        <v>32</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="I13" s="2">
-        <v>10</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="K13" s="2">
-        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/Framework_Inputs/Master_Workbook/Master_Excel.xlsx
+++ b/Framework_Inputs/Master_Workbook/Master_Excel.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nftuser\Documents\FrameworkRepo\Framework_Inputs\Master_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6DA02F6-75D4-4B02-A800-FFB01EC2FE55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00C256DE-EAF0-45CA-B8A7-ACFA4533CF7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{E6EFDEBD-5522-4CFF-85A8-02F11CBA0D33}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{0ED49093-8DC7-485C-8330-103BF7CAEE26}"/>
   </bookViews>
   <sheets>
     <sheet name="Control" sheetId="4" r:id="rId1"/>
@@ -97,13 +97,13 @@
     <t>C:\Users\nftuser\Documents\FrameworkRepo\Framework_Inputs\Scripts\petclinictestplan.jmx</t>
   </si>
   <si>
-    <t>30% Volume</t>
+    <t>60% Volume</t>
   </si>
   <si>
     <t>Yes</t>
   </si>
   <si>
-    <t>127.0.0.1</t>
+    <t>Nil</t>
   </si>
   <si>
     <t>petclinictestplan_Duration</t>
@@ -169,7 +169,7 @@
     <t>Home_Page</t>
   </si>
   <si>
-    <t>Search _For_Vets</t>
+    <t>Search_For_Vets</t>
   </si>
   <si>
     <t>Owners</t>
@@ -187,16 +187,16 @@
     <t>Home_PageRampUp</t>
   </si>
   <si>
-    <t>Search _For_VetsThread</t>
-  </si>
-  <si>
-    <t>Search _For_VetsLoop</t>
-  </si>
-  <si>
-    <t>Search _For_VetsPacing</t>
-  </si>
-  <si>
-    <t>Search _For_VetsRampUp</t>
+    <t>Search_For_VetsThread</t>
+  </si>
+  <si>
+    <t>Search_For_VetsLoop</t>
+  </si>
+  <si>
+    <t>Search_For_VetsPacing</t>
+  </si>
+  <si>
+    <t>Search_For_VetsRampUp</t>
   </si>
   <si>
     <t>OwnersThread</t>
@@ -613,8 +613,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1FB16C5-4791-456B-A841-295FAB02979B}">
-  <sheetPr codeName="Sheet4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFBB7756-527E-4BF5-AD67-BEF86EE1AEAF}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -665,8 +664,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D86495F-CA2A-45F3-88B0-759EE8980182}">
-  <sheetPr codeName="Sheet3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0226F27D-7D26-4BC9-B76D-A73A34FD5BD4}">
   <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -694,7 +692,7 @@
         <v>19</v>
       </c>
       <c r="C2" s="1">
-        <v>3600</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -835,21 +833,20 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57E99092-B274-43C6-83BB-66E13CE8B82B}">
-  <sheetPr codeName="Sheet2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B777ACA-CF35-4850-A8FC-1365CCB36756}">
   <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -902,7 +899,7 @@
         <v>45</v>
       </c>
       <c r="E2" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>46</v>
@@ -920,7 +917,7 @@
         <v>48</v>
       </c>
       <c r="K2" s="2">
-        <v>36</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -937,7 +934,7 @@
         <v>49</v>
       </c>
       <c r="E3" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>50</v>
@@ -955,7 +952,7 @@
         <v>52</v>
       </c>
       <c r="K3" s="2">
-        <v>72</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -972,7 +969,7 @@
         <v>53</v>
       </c>
       <c r="E4" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>54</v>
@@ -990,7 +987,7 @@
         <v>56</v>
       </c>
       <c r="K4" s="2">
-        <v>72</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/Framework_Inputs/Master_Workbook/Master_Excel.xlsx
+++ b/Framework_Inputs/Master_Workbook/Master_Excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nftuser\Documents\FrameworkRepo\Framework_Inputs\Master_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00C256DE-EAF0-45CA-B8A7-ACFA4533CF7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D07D67D3-88BE-4C78-9A3B-F4C1D2331A0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{0ED49093-8DC7-485C-8330-103BF7CAEE26}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{54776139-7EEA-4A55-A930-FDA4F7DB49B2}"/>
   </bookViews>
   <sheets>
     <sheet name="Control" sheetId="4" r:id="rId1"/>
@@ -613,7 +613,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFBB7756-527E-4BF5-AD67-BEF86EE1AEAF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2077383-983B-4208-9FD3-A9FEF1979208}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -664,7 +664,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0226F27D-7D26-4BC9-B76D-A73A34FD5BD4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6162E89-2099-48F0-97E6-AE8747468452}">
   <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -833,7 +833,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B777ACA-CF35-4850-A8FC-1365CCB36756}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D4DEB82-1DE6-4112-BDA7-82FE8AF9371E}">
   <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
